--- a/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Carta Gantt CuTuCo.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Carta Gantt CuTuCo.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignac\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ignac\Videos\Inicio\Evidencias de Documentación\Documentos Actualizados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6248D8-D3BD-4199-91D3-6646C492B838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD50E251-A74A-4B28-B472-A44EF31790A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Analisis de Ingresos" sheetId="1" r:id="rId1"/>
     <sheet name="Carta Gantt" sheetId="2" r:id="rId2"/>
-    <sheet name="EDT v" sheetId="3" r:id="rId3"/>
+    <sheet name="EDT" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="131">
   <si>
     <t>EXPERIENCIA</t>
   </si>
@@ -136,7 +136,7 @@
     <t>Dic.</t>
   </si>
   <si>
-    <t>Fase 1: Planificación inicial</t>
+    <t>Fase 1: Planificación inicial (bloque EDT 1.0)</t>
   </si>
   <si>
     <t>Inicio del proyecto y confirmación del alcance validado</t>
@@ -154,7 +154,7 @@
     <t>Plan de Pruebas Inicial (estrategia y matriz de casos)</t>
   </si>
   <si>
-    <t>Fase 2: Análisis y diseño</t>
+    <t>Fase 2: Análisis y diseño (bloque EDT 2.0)</t>
   </si>
   <si>
     <t>ERS y criterios de aceptación</t>
@@ -163,7 +163,7 @@
     <t>Ajuste de requerimientos al alcance actualizado (Queda / No queda)</t>
   </si>
   <si>
-    <t>Modelo de datos: DER, tabla payouts, RLS y policies</t>
+    <t>Modelo de datos: DER, tablas productores (rut_oficial, codigo_comercio_mall) y payments, RLS y policies</t>
   </si>
   <si>
     <t>Arquitectura: Supabase (GoTrue, PostgREST), FastAPI y despliegue</t>
@@ -178,7 +178,7 @@
     <t>Diseño de casos de prueba</t>
   </si>
   <si>
-    <t>Fase 3: Construcción</t>
+    <t>Fase 3: Construcción (bloques EDT 3.0, 4.0 y 5.0)</t>
   </si>
   <si>
     <t>Base técnica: Git, FastAPI + Docker, Cloud Run y Vue + Vite</t>
@@ -193,7 +193,7 @@
     <t>Autenticación y roles con GoTrue; bloqueo tras 5 intentos (FastAPI)</t>
   </si>
   <si>
-    <t>Registro de cliente y productor; aprobación de productores</t>
+    <t>Registro de cliente y productor; aprobación de productores con Código de Comercio Mall</t>
   </si>
   <si>
     <t>Catálogo con acceso invitado, buscador y carrito (Vue.js)</t>
@@ -208,10 +208,10 @@
     <t>Restricción de venta por región del productor y del cliente</t>
   </si>
   <si>
-    <t>Pago con Webpay Plus Test (create, token_ws, commit) e idempotencia</t>
-  </si>
-  <si>
-    <t>Custodia, tabla payouts, payouts manuales y reembolsos</t>
+    <t>Pago con Webpay Mall (Split Payment: create, token_ws, commit) e idempotencia</t>
+  </si>
+  <si>
+    <t>Liquidación directa por pasarela (Split Payment) y reembolsos</t>
   </si>
   <si>
     <t>Checkout y seguimiento del pedido (Vue.js)</t>
@@ -244,7 +244,7 @@
     <t>Verificación de alcances</t>
   </si>
   <si>
-    <t>Fase 4: Implementación y cierre</t>
+    <t>Fase 4: Implementación y cierre (bloque EDT 6.0)</t>
   </si>
   <si>
     <t>Pruebas de integración de la API REST</t>
@@ -307,7 +307,7 @@
     <t>COSTO x HORA</t>
   </si>
   <si>
-    <t>Fase 1: Planificación inicial (Semana 1)</t>
+    <t>Fase 1: Planificación inicial (Semana 1) — Bloque EDT 1.0 (Gestión del proyecto)</t>
   </si>
   <si>
     <t>JEFE DE PROYECTO</t>
@@ -325,64 +325,64 @@
     <t>1.2 Acta de Constitución, EDT, Hitos de Desarrollo y Diccionario</t>
   </si>
   <si>
-    <t>1.3 Carta Gantt, Matriz RACI y Matriz de Riesgos</t>
-  </si>
-  <si>
-    <t>1.4 Plan de Pruebas Inicial (estrategia y matriz de casos)</t>
-  </si>
-  <si>
-    <t>Fase 2: Análisis y diseño (Semanas 2 a 4)</t>
+    <t>1.2 Carta Gantt, Matriz RACI y Matriz de Riesgos</t>
+  </si>
+  <si>
+    <t>1.2 Plan de Pruebas Inicial (estrategia y matriz de casos)</t>
+  </si>
+  <si>
+    <t>Fase 2: Análisis y diseño (Semanas 2 a 4) — Bloque EDT 2.0 (Análisis y diseño)</t>
   </si>
   <si>
     <t>2.1 ERS, criterios de aceptación y ajuste de requerimientos (Queda / No queda)</t>
   </si>
   <si>
-    <t>2.2 Modelo de datos (DER, payouts, RLS) y arquitectura de la solución</t>
-  </si>
-  <si>
-    <t>2.3 Mockups Vue.js: cliente, productor, administración, checkout y entrega</t>
-  </si>
-  <si>
-    <t>2.4 Plan de Calidad y de Costos; diseño de casos de prueba</t>
-  </si>
-  <si>
-    <t>Fase 3: Construcción (Semanas 4 a 10)</t>
-  </si>
-  <si>
-    <t>3.1 Base técnica: Git, FastAPI + Docker, Cloud Run, Supabase y Vue + Vite</t>
-  </si>
-  <si>
-    <t>3.2 Migración SQLite a PostgreSQL, DDL, RLS y autenticación con GoTrue</t>
-  </si>
-  <si>
-    <t>3.3 Catálogo invitado, carrito, registro, panel productor y CRUD base (PostgREST)</t>
-  </si>
-  <si>
-    <t>3.4 Webpay Plus Test, custodia, payouts manuales, reembolsos y checkout</t>
-  </si>
-  <si>
-    <t>3.5 Entrega con código, venta por región, calificaciones, sanciones y correos</t>
-  </si>
-  <si>
-    <t>3.6 Dashboard admin, validaciones (Vuelidate) y pruebas unitarias</t>
+    <t>2.2 / 2.3 Modelo de datos (DER, productores, payments, RLS) y arquitectura de la solución</t>
+  </si>
+  <si>
+    <t>2.4 Mockups Vue.js: cliente, productor, administración, checkout y entrega</t>
+  </si>
+  <si>
+    <t>2.5 Plan de Calidad y de Costos; diseño de casos de prueba</t>
+  </si>
+  <si>
+    <t>Fase 3: Construcción (Semanas 4 a 10) — Bloques EDT 3.0, 4.0 y 5.0</t>
+  </si>
+  <si>
+    <t>3.1 / 4.1 / 5.1 - 5.3 Base técnica: Git, FastAPI + Docker, Cloud Run, Supabase y Vue + Vite</t>
+  </si>
+  <si>
+    <t>3.2 / 3.7 / 5.1 Migración SQLite a PostgreSQL, DDL, RLS y autenticación con GoTrue</t>
+  </si>
+  <si>
+    <t>3.3 / 4.2 / 4.3 Catálogo invitado, carrito, registro, panel productor y CRUD base (PostgREST)</t>
+  </si>
+  <si>
+    <t>3.4 / 4.5 Webpay Mall (Split Payment), liquidación por pasarela, reembolsos y checkout</t>
+  </si>
+  <si>
+    <t>3.5 / 3.6 / 4.4 Entrega con código, venta por región, calificaciones, sanciones y correos</t>
+  </si>
+  <si>
+    <t>4.4 / 4.6 / 6.1 Dashboard admin, validaciones (Vuelidate) y pruebas unitarias</t>
   </si>
   <si>
     <t>COSTO HH POR ROL</t>
   </si>
   <si>
-    <t>Fase 4: Implementación y cierre (Semanas 11 a 13)</t>
-  </si>
-  <si>
-    <t>4.1 Pruebas de integración API y E2E, correcciones y verificación de alcances</t>
-  </si>
-  <si>
-    <t>4.2 Despliegue final (Vercel, Cloud Run, Supabase) y pruebas de humo</t>
-  </si>
-  <si>
-    <t>4.3 Plan de Implantación, Soporte y Mantenimiento; Manuales de Usuario/Admin</t>
-  </si>
-  <si>
-    <t>4.4 Plan de Pruebas Final, Reporte de Estatus Final y entrega final</t>
+    <t>Fase 4: Implementación y cierre (Semanas 11 a 13) — Bloque EDT 6.0</t>
+  </si>
+  <si>
+    <t>6.1 / 6.2 / 6.4 / 6.5 Pruebas de integración API y E2E, correcciones y verificación de alcances</t>
+  </si>
+  <si>
+    <t>5.2 / 5.3 / 5.5 / 6.4 Despliegue final (Vercel, Cloud Run, Supabase) y pruebas de humo</t>
+  </si>
+  <si>
+    <t>6.6 Plan de Implantación, Soporte y Mantenimiento; Manuales de Usuario/Admin</t>
+  </si>
+  <si>
+    <t>6.3 / 6.6 / 6.7 Plan de Pruebas Final, Reporte de Estatus Final y entrega final</t>
   </si>
   <si>
     <t>Dias</t>
@@ -413,6 +413,24 @@
   </si>
   <si>
     <t>Sin geolocalización, fotos obligatorias ni cosecha del día: la entrega se confirma con código y las sanciones son manuales.</t>
+  </si>
+  <si>
+    <t>Correspondencia entre los bloques de la EDT (6 bloques, 34 paquetes) y las 4 fases del proyecto (Acta de Constitución):</t>
+  </si>
+  <si>
+    <t>Fase 1: Planificación inicial — bloque EDT 1.0 (Gestión del proyecto), paquetes 1.1 a 1.4, semanas 1 a 2.</t>
+  </si>
+  <si>
+    <t>Fase 2: Análisis y diseño — bloque EDT 2.0 (Análisis y diseño), paquetes 2.1 a 2.5, semanas 2 a 4.</t>
+  </si>
+  <si>
+    <t>Fase 3: Construcción — bloques EDT 3.0 (backend y datos), 4.0 (frontend) y 5.0 (infraestructura, integración y CI/CD); paquetes 3.1 a 3.7, 4.1 a 4.6 y 5.1 a 5.5, semanas 4 a 10 (se ejecutan en paralelo).</t>
+  </si>
+  <si>
+    <t>Fase 4: Implementación y cierre — bloque EDT 6.0 (Pruebas, implementación y cierre), paquetes 6.1 a 6.7, semanas 10 a 13.</t>
+  </si>
+  <si>
+    <t>Las actividades de cada fase citan los paquetes EDT que cubren; las horas y los días se mantienen igual.</t>
   </si>
 </sst>
 </file>
@@ -589,7 +607,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -726,11 +744,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -750,9 +781,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -763,17 +791,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -796,9 +816,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -821,6 +838,30 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1259,7 +1300,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC1002"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.625" style="8" customWidth="1"/>
@@ -1271,254 +1315,211 @@
     <col min="27" max="16384" width="12.625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5">
         <v>1</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="10"/>
       <c r="E3" s="3">
         <v>1800000</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <f t="shared" ref="F3:F8" si="0">(E3*19/100)+E3</f>
         <v>2142000</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="37">
         <f t="shared" ref="G3:G8" si="1">F3/160</f>
         <v>13387.5</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="38" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="13"/>
       <c r="E4" s="1">
         <v>800000</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <f t="shared" si="0"/>
         <v>952000</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="37">
         <f t="shared" si="1"/>
         <v>5950</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="17"/>
-      <c r="Z4" s="15"/>
-      <c r="AA4" s="17"/>
-      <c r="AB4" s="15"/>
-      <c r="AC4" s="17"/>
-    </row>
-    <row r="5" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="18"/>
+      <c r="D5" s="15"/>
       <c r="E5" s="2">
         <v>1500000</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <f t="shared" si="0"/>
         <v>1785000</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="37">
         <f t="shared" si="1"/>
         <v>11156.25</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
-      <c r="V5" s="18"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="18"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="18"/>
-      <c r="AC5" s="18"/>
-    </row>
-    <row r="6" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="4">
         <v>1350000</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <f t="shared" si="0"/>
         <v>1606500</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="37">
         <f t="shared" si="1"/>
         <v>10040.625</v>
       </c>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="I6" s="38"/>
+    </row>
+    <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="17"/>
+      <c r="D7" s="14"/>
       <c r="E7" s="4">
         <v>1000000</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <f t="shared" si="0"/>
         <v>1190000</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="37">
         <f t="shared" si="1"/>
         <v>7437.5</v>
       </c>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="I7" s="38"/>
+    </row>
+    <row r="8" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="4">
         <v>1300000</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <f t="shared" si="0"/>
         <v>1547000</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="37">
         <f t="shared" si="1"/>
         <v>9668.75</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="38" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:29" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2514,9 +2515,9 @@
     <hyperlink ref="I4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="I8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId4"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="48" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -2534,956 +2535,956 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="11">
+      <c r="B1" s="10">
         <v>1</v>
       </c>
-      <c r="C1" s="11">
+      <c r="C1" s="10">
         <v>2</v>
       </c>
-      <c r="D1" s="11">
+      <c r="D1" s="10">
         <v>3</v>
       </c>
-      <c r="E1" s="11">
+      <c r="E1" s="10">
         <v>4</v>
       </c>
-      <c r="F1" s="11">
+      <c r="F1" s="10">
         <v>5</v>
       </c>
-      <c r="G1" s="11">
+      <c r="G1" s="10">
         <v>6</v>
       </c>
-      <c r="H1" s="11">
+      <c r="H1" s="10">
         <v>7</v>
       </c>
-      <c r="I1" s="11">
+      <c r="I1" s="10">
         <v>8</v>
       </c>
-      <c r="J1" s="11">
+      <c r="J1" s="10">
         <v>9</v>
       </c>
-      <c r="K1" s="11">
+      <c r="K1" s="10">
         <v>10</v>
       </c>
-      <c r="L1" s="11">
+      <c r="L1" s="10">
         <v>11</v>
       </c>
-      <c r="M1" s="11">
+      <c r="M1" s="10">
         <v>12</v>
       </c>
-      <c r="N1" s="11">
+      <c r="N1" s="10">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20" t="s">
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="11" t="s">
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+    </row>
+    <row r="12" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+    </row>
+    <row r="22" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="45"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="17"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="14"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="23"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="17"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="14"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="23"/>
-      <c r="N44" s="17"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="14"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="17"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="14"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="14"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
-      <c r="N47" s="23"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="16"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22"/>
-      <c r="N48" s="22"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
+      <c r="M48" s="45"/>
+      <c r="N48" s="45"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
-      <c r="J50" s="23"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="23"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
+      <c r="A51" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="23"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
     </row>
     <row r="65" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="66" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -3504,12 +3505,15 @@
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="65" pageOrder="overThenDown" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M886"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3532,804 +3536,804 @@
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="J2" s="27" t="s">
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="J2" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="L2" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="19">
         <f>SUM(B4:B7)</f>
         <v>5</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="12">
         <f>'Analisis de Ingresos'!G3</f>
         <v>13387.5</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="19">
         <v>1</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="23">
         <v>4</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="23">
         <v>3</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="23">
         <v>0</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="23">
         <v>0</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="23">
         <v>0</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="23">
         <v>0</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="J4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="24">
         <f>'Analisis de Ingresos'!G4</f>
         <v>5950</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="19">
         <v>2</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="23">
         <v>8</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="23">
         <v>6</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="23">
         <v>2</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="23">
         <v>0</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="23">
         <v>0</v>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="23">
         <v>0</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="M5" s="32">
+      <c r="M5" s="25">
         <f>'Analisis de Ingresos'!G5</f>
         <v>11156.25</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="19">
         <v>1</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="23">
         <v>4</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="23">
         <v>3</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="23">
         <v>0</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="23">
         <v>0</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="23">
         <v>0</v>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="23">
         <v>0</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="M6" s="32">
+      <c r="M6" s="25">
         <f>'Analisis de Ingresos'!G6</f>
         <v>10040.625</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="19">
         <v>1</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="23">
         <v>2</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="23">
         <v>5</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="23">
         <v>0</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="23">
         <v>0</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="23">
         <v>2</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="23">
         <v>2</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="12">
         <f>'Analisis de Ingresos'!G7</f>
         <v>7437.5</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="19">
         <f>SUM(B9:B12)</f>
         <v>10</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="17" t="s">
+      <c r="L8" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="12">
         <f>'Analisis de Ingresos'!G8</f>
         <v>9668.75</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="19">
         <v>3</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="23">
         <v>6</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="23">
         <v>12</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="23">
         <v>4</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="23">
         <v>0</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="23">
         <v>4</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="19">
         <v>3</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="23">
         <v>4</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="23">
         <v>0</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="23">
         <v>14</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="23">
         <v>16</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="23">
         <v>4</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="23">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="19">
         <v>2</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="23">
         <v>2</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="23">
         <v>12</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="23">
         <v>0</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="23">
         <v>0</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="23">
         <v>0</v>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="19">
         <v>2</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="23">
         <v>6</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="23">
         <v>8</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="23">
         <v>2</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="23">
         <v>0</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="23">
         <v>2</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="23">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="19">
         <f>SUM(B14:B19)</f>
         <v>35</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="29" t="s">
+      <c r="H13" s="22" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="19">
         <v>5</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="23">
         <v>4</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="23">
         <v>0</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="23">
         <v>6</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="23">
         <v>4</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="23">
         <v>14</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="23">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="19">
         <v>5</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="23">
         <v>3</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="23">
         <v>0</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="23">
         <v>4</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="23">
         <v>20</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="23">
         <v>14</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="19">
         <v>7</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="23">
         <v>3</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="23">
         <v>0</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="23">
         <v>2</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="23">
         <v>4</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="23">
         <v>14</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="23">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="19">
         <v>6</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="23">
         <v>4</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="23">
         <v>0</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="23">
         <v>2</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="23">
         <v>6</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="23">
         <v>26</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="23">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="19">
         <v>6</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="23">
         <v>3</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="23">
         <v>0</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="23">
         <v>0</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="23">
         <v>2</v>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="23">
         <v>22</v>
       </c>
-      <c r="H18" s="30">
+      <c r="H18" s="23">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="19">
         <v>6</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="23">
         <v>3</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="23">
         <v>4</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="23">
         <v>0</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="23">
         <v>0</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="23">
         <v>8</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="23">
         <v>24</v>
       </c>
-      <c r="J19" s="33" t="s">
+      <c r="J19" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="33"/>
+      <c r="K19" s="43"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="19">
         <f>SUM(B21:B24)</f>
         <v>15</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F20" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="35" t="s">
+      <c r="H20" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="17" t="s">
+      <c r="J20" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="36">
+      <c r="K20" s="28">
         <f>$M$3*C26</f>
         <v>990675</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="19">
         <v>5</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="23">
         <v>4</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="23">
         <v>14</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="23">
         <v>0</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="23">
         <v>0</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="23">
         <v>14</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="23">
         <v>14</v>
       </c>
-      <c r="J21" s="17" t="s">
+      <c r="J21" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="36">
+      <c r="K21" s="28">
         <f>$M$4*D26</f>
         <v>541450</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="19">
         <v>2</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="23">
         <v>2</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="23">
         <v>0</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="23">
         <v>2</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="23">
         <v>2</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="23">
         <v>6</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="23">
         <v>4</v>
       </c>
-      <c r="J22" s="18" t="s">
+      <c r="J22" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="28">
         <f>$M$5*E26</f>
         <v>446250</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="19">
         <v>3</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="23">
         <v>4</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="23">
         <v>14</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="23">
         <v>2</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="23">
         <v>2</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="23">
         <v>4</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="23">
         <v>8</v>
       </c>
-      <c r="J23" s="18" t="s">
+      <c r="J23" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="K23" s="36">
+      <c r="K23" s="28">
         <f>$M$6*F26</f>
         <v>562275</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="19">
         <v>5</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="23">
         <v>8</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="23">
         <v>10</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="23">
         <v>0</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="23">
         <v>0</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="23">
         <v>4</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="23">
         <v>4</v>
       </c>
-      <c r="J24" s="17" t="s">
+      <c r="J24" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="28">
         <f>$M$7*G26</f>
         <v>1026375</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="37"/>
-      <c r="B25" s="38" t="s">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="35" t="s">
+      <c r="H25" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="17" t="s">
+      <c r="J25" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="K25" s="36">
+      <c r="K25" s="28">
         <f>$M$8*H26</f>
         <v>1527662.5</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="32">
         <f>B3+B8+B13+B20</f>
         <v>65</v>
       </c>
-      <c r="C26" s="40">
+      <c r="C26" s="32">
         <f t="shared" ref="C26:H26" si="0">SUM(C4:C7)+SUM(C9:C12)+SUM(C14:C19)+SUM(C21:C24)</f>
         <v>74</v>
       </c>
-      <c r="D26" s="40">
+      <c r="D26" s="32">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="32">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="32">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="32">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="H26" s="40">
+      <c r="H26" s="32">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
-      <c r="J26" s="41" t="s">
+      <c r="J26" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="K26" s="42">
+      <c r="K26" s="34">
         <f>SUM(K20:K25)</f>
         <v>5094687.5</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="35" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4364,12 +4368,36 @@
       </c>
     </row>
     <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="35" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
     <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5221,6 +5249,6 @@
     <mergeCell ref="J19:K19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="39" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Carta Gantt CuTuCo.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de Documentación/Carta Gantt CuTuCo.xlsx
@@ -163,13 +163,13 @@
     <t>Ajuste de requerimientos al alcance actualizado (Queda / No queda)</t>
   </si>
   <si>
-    <t>Modelo de datos: DER, tablas productores (rut_oficial, codigo_comercio_mall) y payments, RLS y policies</t>
-  </si>
-  <si>
-    <t>Arquitectura: Supabase (GoTrue, PostgREST), FastAPI y despliegue</t>
-  </si>
-  <si>
-    <t>Mockups de interfaz Vue.js (cliente, productor y administración)</t>
+    <t>Modelo de datos: MER, tablas productores (rut_oficial, codigo_comercio_mall) y payments, RLS y policies</t>
+  </si>
+  <si>
+    <t>Arquitectura: Supabase (GoTrue, PostgREST), FastAPI solo para Webpay y despliegue</t>
+  </si>
+  <si>
+    <t>Mockups de interfaz Vue.js (cliente, productor, administración y reclamos)</t>
   </si>
   <si>
     <t>Plan de Calidad y de Costos</t>
@@ -190,16 +190,16 @@
     <t>Migración SQLite a PostgreSQL y scripts de creación (DDL)</t>
   </si>
   <si>
-    <t>Autenticación y roles con GoTrue; bloqueo tras 5 intentos (FastAPI)</t>
-  </si>
-  <si>
-    <t>Registro de cliente y productor; aprobación de productores con Código de Comercio Mall</t>
+    <t>Autenticación, roles y permisos con GoTrue, RLS y policies (Supabase Auth)</t>
+  </si>
+  <si>
+    <t>Registro de cliente y productor; aprobación de postulaciones y registro del Código de Comercio Mall</t>
   </si>
   <si>
     <t>Catálogo con acceso invitado, buscador y carrito (Vue.js)</t>
   </si>
   <si>
-    <t>Consultas por PostgREST: productos, pedidos, usuarios y categorías</t>
+    <t>Consultas por PostgREST: productos, pedidos, usuarios, categorías y reclamos</t>
   </si>
   <si>
     <t>Panel del productor: productos, stock y ventas</t>
@@ -211,22 +211,22 @@
     <t>Pago con Webpay Mall (Split Payment: create, token_ws, commit) e idempotencia</t>
   </si>
   <si>
-    <t>Liquidación directa por pasarela (Split Payment) y reembolsos</t>
-  </si>
-  <si>
-    <t>Checkout y seguimiento del pedido (Vue.js)</t>
-  </si>
-  <si>
-    <t>Panel de administración y dashboard (aprobaciones, sanciones, pagos)</t>
+    <t>Gestión de reclamos (RF-027): registro, seguimiento, resolución y apelaciones</t>
+  </si>
+  <si>
+    <t>Checkout, seguimiento del pedido y registro de reclamos (Vue.js)</t>
+  </si>
+  <si>
+    <t>Panel de administración y dashboard (aprobaciones, reclamos, sanciones y pagos)</t>
   </si>
   <si>
     <t>Entrega con código de verificación (Preparación, En Tránsito, Entregado)</t>
   </si>
   <si>
-    <t>Calificaciones de 1 a 5, promedio y sanciones manuales</t>
-  </si>
-  <si>
-    <t>Correos con Resend (Auth por SMTP de Supabase y notificaciones)</t>
+    <t>Calificaciones de 1 a 5, promedio, sanciones manuales y apelaciones</t>
+  </si>
+  <si>
+    <t>Correos con Resend (autenticación por el SMTP de Supabase, detalle de compra y aviso de nuevo pedido)</t>
   </si>
   <si>
     <t>Validaciones: Vuelidate en frontend y Pydantic/constraints en backend</t>
@@ -250,7 +250,7 @@
     <t>Pruebas de integración de la API REST</t>
   </si>
   <si>
-    <t>Pruebas E2E de flujos críticos (compra, pago, entrega, calificación)</t>
+    <t>Pruebas E2E de flujos críticos (compra, pago, entrega, calificación y reclamo)</t>
   </si>
   <si>
     <t>Corrección de defectos y regresión</t>
@@ -337,7 +337,7 @@
     <t>2.1 ERS, criterios de aceptación y ajuste de requerimientos (Queda / No queda)</t>
   </si>
   <si>
-    <t>2.2 / 2.3 Modelo de datos (DER, productores, payments, RLS) y arquitectura de la solución</t>
+    <t>2.2 / 2.3 Modelo de datos (MER, productores, payments, RLS) y arquitectura de la solución</t>
   </si>
   <si>
     <t>2.4 Mockups Vue.js: cliente, productor, administración, checkout y entrega</t>
@@ -358,13 +358,13 @@
     <t>3.3 / 4.2 / 4.3 Catálogo invitado, carrito, registro, panel productor y CRUD base (PostgREST)</t>
   </si>
   <si>
-    <t>3.4 / 4.5 Webpay Mall (Split Payment), liquidación por pasarela, reembolsos y checkout</t>
-  </si>
-  <si>
-    <t>3.5 / 3.6 / 4.4 Entrega con código, venta por región, calificaciones, sanciones y correos</t>
-  </si>
-  <si>
-    <t>4.4 / 4.6 / 6.1 Dashboard admin, validaciones (Vuelidate) y pruebas unitarias</t>
+    <t>3.4 / 4.5 Webpay Mall (Split Payment), dispersión por pasarela y checkout</t>
+  </si>
+  <si>
+    <t>3.5 / 3.6 / 4.4 Entrega con código, venta por región, calificaciones, reclamos (RF-027), sanciones y correos</t>
+  </si>
+  <si>
+    <t>4.4 / 4.6 / 6.1 Dashboard admin (reclamos y sanciones), validaciones (Vuelidate) y pruebas unitarias</t>
   </si>
   <si>
     <t>COSTO HH POR ROL</t>
@@ -409,10 +409,10 @@
     <t>El costo por hora usa sueldos referenciales (hoja Analisis de Ingresos); no son pagos reales del proyecto.</t>
   </si>
   <si>
-    <t>Alcance actualizado: no planificamos historial de precios, stock bajo, múltiples admins, retención de carnet ni rate limiting.</t>
-  </si>
-  <si>
-    <t>Sin geolocalización, fotos obligatorias ni cosecha del día: la entrega se confirma con código y las sanciones son manuales.</t>
+    <t>Alcance actualizado: no planificamos historial de precios, avisos de stock bajo, múltiples administradores ni rate limiting propio, y RF-015 (almacenamiento de datos sensibles, como el carnet de identidad) queda eliminado.</t>
+  </si>
+  <si>
+    <t>Sin geolocalización, fotos obligatorias ni cosecha del día: la entrega se confirma con código, la validación de palabras prohibidas es automática por triggers y las sanciones son manuales, con reclamos y apelaciones (RF-027).</t>
   </si>
   <si>
     <t>Correspondencia entre los bloques de la EDT (6 bloques, 34 paquetes) y las 4 fases del proyecto (Acta de Constitución):</t>
